--- a/Equiv/2024/Day_data_conversion.xlsx
+++ b/Equiv/2024/Day_data_conversion.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73511D03-8160-4372-B013-AE112A8E5839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD41AB2A-5E96-4C47-BDF3-D8756A9842B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="travel_dow" sheetId="6" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="51">
   <si>
     <t>Year</t>
   </si>
@@ -225,11 +225,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2477,13 +2475,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B0E0B0-01D7-477E-994E-ADEEF58B0A85}">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2497,7 +2495,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2021</v>
       </c>
@@ -2511,7 +2509,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2021</v>
       </c>
@@ -2524,44 +2522,8 @@
       <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1641711</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1678042</v>
-      </c>
-      <c r="K3" s="2">
-        <v>155958</v>
-      </c>
-      <c r="L3" s="2">
-        <v>7796</v>
-      </c>
-      <c r="M3" s="2">
-        <v>31038</v>
-      </c>
-      <c r="N3" s="3">
-        <v>0.877</v>
-      </c>
-      <c r="O3" s="3">
-        <v>0.88300000000000001</v>
-      </c>
-      <c r="P3" s="3">
-        <v>0.47199999999999998</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="R3" s="3">
-        <v>0.44500000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2021</v>
       </c>
@@ -2574,44 +2536,8 @@
       <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="2">
-        <v>229707</v>
-      </c>
-      <c r="J4" s="2">
-        <v>222238</v>
-      </c>
-      <c r="K4" s="2">
-        <v>174387</v>
-      </c>
-      <c r="L4" s="2">
-        <v>9183</v>
-      </c>
-      <c r="M4" s="2">
-        <v>26520</v>
-      </c>
-      <c r="N4" s="3">
-        <v>0.123</v>
-      </c>
-      <c r="O4" s="3">
-        <v>0.11700000000000001</v>
-      </c>
-      <c r="P4" s="3">
-        <v>0.52800000000000002</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>0.34699999999999998</v>
-      </c>
-      <c r="R4" s="3">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2021</v>
       </c>
@@ -2624,32 +2550,8 @@
       <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="G5">
-        <v>998</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5">
-        <v>34</v>
-      </c>
-      <c r="L5" s="2">
-        <v>2926</v>
-      </c>
-      <c r="M5" s="2">
-        <v>7324</v>
-      </c>
-      <c r="P5" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>0.111</v>
-      </c>
-      <c r="R5" s="3">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2021</v>
       </c>
@@ -2659,26 +2561,8 @@
       <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="G6">
-        <v>999</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="2">
-        <v>6542</v>
-      </c>
-      <c r="M6" s="2">
-        <v>4888</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>0.247</v>
-      </c>
-      <c r="R6" s="3">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2018</v>
       </c>
@@ -2691,23 +2575,8 @@
       <c r="D7" t="s">
         <v>19</v>
       </c>
-      <c r="G7">
-        <v>995</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1635853</v>
-      </c>
-      <c r="L7" s="2">
-        <v>2034171</v>
-      </c>
-      <c r="M7" s="2">
-        <v>2089323</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2018</v>
       </c>
@@ -2721,7 +2590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2018</v>
       </c>
@@ -2735,7 +2604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -2749,7 +2618,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2018</v>
       </c>
@@ -2760,7 +2629,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2024</v>
       </c>
@@ -2774,7 +2643,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2024</v>
       </c>
@@ -2788,7 +2657,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2024</v>
       </c>
@@ -2802,7 +2671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2024</v>
       </c>
@@ -2816,7 +2685,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
